--- a/data/mapas/Mapa_de_Carrera_Historia.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Historia.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B56, "SI")</f>
+        <f>COUNTIF(B6:B42, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C56, "SI")</f>
+        <f>COUNTIF(C6:C42, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F56, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F42, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Historia. ARGENTINA Y AMERICANA I</t>
+          <t>Introducción a la Historia</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B56, "SI")/45</f>
+        <f>COUNTIF(B6:B42, "SI")/33</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Introducción. A LA Historia. ANTIGUA</t>
+          <t>Historia Antigua de Oriente y Grecia</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C56, "SI")/45</f>
+        <f>COUNTIF(C6:C42, "SI")/33</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Introduccion a la Historia</t>
+          <t>Historia Antigua de Roma</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Historia de América I (Precolombina e Indígena)</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía GENERAL</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Prehistoria y Arqueologia</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -948,37 +948,10 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Trabajo de Campo I</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>1° Año</t>
-        </is>
-      </c>
-      <c r="E13" s="10">
-        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -987,10 +960,37 @@
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Historia Medieval</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E14" s="10">
+        <f>IF(B14="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F14" s="10">
+        <f>IF(C14="SI", "APROBADO", IF(B14="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G14" s="11">
+        <f>IF(C14="SI", "🟢 Aprobada", IF(B14="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I14" s="14" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Didáctica GENERAL</t>
+          <t>Historia Moderna</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1040,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Historia. ARGENTINA Y AMERICANA II</t>
+          <t>Historia de América II (Colonial)</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Historia de España</t>
+          <t>Historia Argentina I (Colonial e Independencia)</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Historia de Grecia</t>
+          <t>Didáctica General</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Historia de Roma</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Sujetos de la Educación</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1207,51 +1207,51 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="7" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Trabajo de Campo II</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E21" s="10">
+        <f>IF(B21="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F21" s="10">
+        <f>IF(C21="SI", "APROBADO", IF(B21="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G21" s="11">
+        <f>IF(C21="SI", "🟢 Aprobada", IF(B21="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>📌 3° AÑO</t>
         </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Construcción de la Práctica Docente. / ENSEÑANZA DE LA Historia</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E22" s="10">
-        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G22" s="11">
-        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Historia Argentina y Americana III</t>
+          <t>Historia Contemporánea del Siglo XIX</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Historia de la Edad Media</t>
+          <t>Historia de América III (Siglo XIX)</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Historia de la Edad Moderna</t>
+          <t>Historia Argentina II (Siglo XIX)</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>INTRODUCCION A LA Geografía</t>
+          <t>Didáctica de la Historia I</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Psicología EDUCACIONAL</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Sujeto de Nivel</t>
+          <t>Derechos Humanos, Sociedad y Estado</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1452,51 +1452,51 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la Práctica Docente I</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E29" s="10">
+        <f>IF(B29="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F29" s="10">
+        <f>IF(C29="SI", "APROBADO", IF(B29="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G29" s="11">
+        <f>IF(C29="SI", "🟢 Aprobada", IF(B29="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
         <is>
           <t>📌 4° AÑO</t>
         </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>Filosofía</t>
-        </is>
-      </c>
-      <c r="B30" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D30" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E30" s="10">
-        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F30" s="10">
-        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G30" s="11">
-        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Historia Americana Contemporanea</t>
+          <t>Historia Contemporánea del Siglo XX</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1530,7 +1530,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Historia Argentina Contemporanea</t>
+          <t>Historia de América IV (Siglo XX y Actual)</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1564,7 +1564,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Historia Contemporanea</t>
+          <t>Historia Argentina III (Siglo XX y Actual)</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1598,7 +1598,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>PRACT. DOC. II y Residencia MEDIA Y SUP</t>
+          <t>Historiografía</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1632,7 +1632,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Metod. Invest / Residencia</t>
+          <t>Didáctica de la Historia II</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1663,17 +1663,44 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Educación Sexual Integral (ESI)</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E36" s="10">
+        <f>IF(B36="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>IF(C36="SI", "APROBADO", IF(B36="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G36" s="11">
+        <f>IF(C36="SI", "🟢 Aprobada", IF(B36="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Dd.hh., Sociedad y Estado</t>
+          <t>Ética y Trabajo Docente</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1688,7 +1715,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1707,7 +1734,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Educación SEXUAL INTEGRAL (cuatrim.)</t>
+          <t>Residencia y Construcción de la Práctica Docente II</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1722,7 +1749,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E38" s="10">
@@ -1738,44 +1765,17 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
-      <c r="A39" s="8" t="inlineStr">
-        <is>
-          <t>HISTORIA DE LA Educación ARGENTINA</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D39" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E39" s="10">
-        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F39" s="10">
-        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G39" s="11">
-        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Historia del Arte</t>
+          <t>Seminario de Historia Argentina y Latinoamericana</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1809,7 +1809,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Lengua Extranjera a (cuatrimestral)</t>
+          <t>Seminario de Historia Mundial Contemporánea</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1843,7 +1843,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>SISTEMA Y Política (CUATRIMESTRAL)</t>
+          <t>Taller de Investigación Histórica</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E42" s="10">
@@ -1874,450 +1874,26 @@
         <v/>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t>Teoría E HISTORIA DE LA HISTORIOG</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D43" s="10" t="inlineStr">
-        <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E43" s="10">
-        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F43" s="10">
-        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G43" s="11">
-        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="8" t="inlineStr">
-        <is>
-          <t>Seminario de Especialización Superior II</t>
-        </is>
-      </c>
-      <c r="B45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C45" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D45" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E45" s="10">
-        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F45" s="10">
-        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G45" s="11">
-        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46" ht="20" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
-        <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
-        </is>
-      </c>
-      <c r="B46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C46" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D46" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E46" s="10">
-        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F46" s="10">
-        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G46" s="11">
-        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
-        <is>
-          <t>Práctica de Nivel Superior II</t>
-        </is>
-      </c>
-      <c r="B47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D47" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E47" s="10">
-        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F47" s="10">
-        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G47" s="11">
-        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
-        <is>
-          <t>Acreditación de Residencia Superior</t>
-        </is>
-      </c>
-      <c r="B48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C48" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D48" s="10" t="inlineStr">
-        <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
-        </is>
-      </c>
-      <c r="E48" s="10">
-        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F48" s="10">
-        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G48" s="11">
-        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>📌 GENERAL / OPTATIVAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>Historia de Africa</t>
-        </is>
-      </c>
-      <c r="B50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D50" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E50" s="10">
-        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F50" s="10">
-        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G50" s="11">
-        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>Historia de Asia</t>
-        </is>
-      </c>
-      <c r="B51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D51" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E51" s="10">
-        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F51" s="10">
-        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G51" s="11">
-        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>Historia de la Edad Media y Tp</t>
-        </is>
-      </c>
-      <c r="B52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C52" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D52" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E52" s="10">
-        <f>IF(B52="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F52" s="10">
-        <f>IF(C52="SI", "APROBADO", IF(B52="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G52" s="11">
-        <f>IF(C52="SI", "🟢 Aprobada", IF(B52="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>Introduccion a la Historia y Tp</t>
-        </is>
-      </c>
-      <c r="B53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D53" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E53" s="10">
-        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F53" s="10">
-        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G53" s="11">
-        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>SEMINARIO DE MET. DE LA Investigación</t>
-        </is>
-      </c>
-      <c r="B54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D54" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E54" s="10">
-        <f>IF(B54="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F54" s="10">
-        <f>IF(C54="SI", "APROBADO", IF(B54="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G54" s="11">
-        <f>IF(C54="SI", "🟢 Aprobada", IF(B54="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Seminario Opt. I</t>
-        </is>
-      </c>
-      <c r="B55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E55" s="10">
-        <f>IF(B55="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F55" s="10">
-        <f>IF(C55="SI", "APROBADO", IF(B55="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G55" s="11">
-        <f>IF(C55="SI", "🟢 Aprobada", IF(B55="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Seminario Optativo II</t>
-        </is>
-      </c>
-      <c r="B56" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C56" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D56" s="10" t="inlineStr">
-        <is>
-          <t>General / Optativas</t>
-        </is>
-      </c>
-      <c r="E56" s="10">
-        <f>IF(B56="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F56" s="10">
-        <f>IF(C56="SI", "APROBADO", IF(B56="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G56" s="11">
-        <f>IF(C56="SI", "🟢 Aprobada", IF(B56="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A36:G36"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A44:G44"/>
+  <mergeCells count="15">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I15:J15"/>
-    <mergeCell ref="A21:G21"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="A39:G39"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
+    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A29:G29"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
-    <mergeCell ref="A49:G49"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B15 B16 B17 B18 B19 B20 B22 B23 B24 B25 B26 B27 B28 B30 B31 B32 B33 B34 B35 B37 B38 B39 B40 B41 B42 B43 B45 B46 B47 B48 B50 B51 B52 B53 B54 B55 B56 C6 C7 C8 C9 C10 C11 C12 C13 C15 C16 C17 C18 C19 C20 C22 C23 C24 C25 C26 C27 C28 C30 C31 C32 C33 C34 C35 C37 C38 C39 C40 C41 C42 C43 C45 C46 C47 C48 C50 C51 C52 C53 C54 C55 C56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B38 B40 B41 B42 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C38 C40 C41 C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Historia.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Historia.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B42, "SI")</f>
+        <f>COUNTIF(B6:B50, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C42, "SI")</f>
+        <f>COUNTIF(C6:C50, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,7 +667,7 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F42, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F50, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B42, "SI")/33</f>
+        <f>COUNTIF(B6:B50, "SI")/40</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Historia Antigua de Oriente y Grecia</t>
+          <t>PreHistoria y Arqueología</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C42, "SI")/33</f>
+        <f>COUNTIF(C6:C50, "SI")/40</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Historia Antigua de Roma</t>
+          <t>Introducción a la Historia Antigua</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Historia de América I (Precolombina e Indígena)</t>
+          <t>Historia Argentina y Americana 1</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Pedagogía General</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -962,7 +962,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Historia Medieval</t>
+          <t>Historia Argentina y Americana 2</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -1001,7 +1001,7 @@
     <row r="15" ht="20" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Historia Moderna</t>
+          <t>Historia de Roma</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
@@ -1040,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Historia de América II (Colonial)</t>
+          <t>Historia de Grecia</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Historia Argentina I (Colonial e Independencia)</t>
+          <t>Historia de España</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Sujetos de la Educación</t>
+          <t>Lectura, Escritura y Oralidad II (LEO 2)</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1207,51 +1207,51 @@
         <v/>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>Trabajo de Campo II</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C21" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D21" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E21" s="10">
-        <f>IF(B21="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F21" s="10">
-        <f>IF(C21="SI", "APROBADO", IF(B21="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G21" s="11">
-        <f>IF(C21="SI", "🟢 Aprobada", IF(B21="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>📌 3° AÑO</t>
         </is>
+      </c>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Historia Argentina y Americana 3</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E22" s="10">
+        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Historia Contemporánea del Siglo XIX</t>
+          <t>Historia de la Edad Media</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1285,7 +1285,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Historia de América III (Siglo XIX)</t>
+          <t>Historia de la Edad Moderna</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1319,7 +1319,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Historia Argentina II (Siglo XIX)</t>
+          <t>Enseñanza de la Historia y Construcción de la Práctica Docente 1</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1353,7 +1353,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Historia I</t>
+          <t>Introducción a la Geografía</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1387,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Psicología Educacional</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1421,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Derechos Humanos, Sociedad y Estado</t>
+          <t>Sujetos del Nivel</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1452,85 +1452,58 @@
         <v/>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>Construcción de la Práctica Docente I</t>
-        </is>
-      </c>
-      <c r="B29" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D29" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E29" s="10">
-        <f>IF(B29="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F29" s="10">
-        <f>IF(C29="SI", "APROBADO", IF(B29="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G29" s="11">
-        <f>IF(C29="SI", "🟢 Aprobada", IF(B29="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>📌 4° AÑO</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>Historia Contemporánea del Siglo XX</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D31" s="10" t="inlineStr">
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Historia Argentina Contemporánea</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
         <is>
           <t>4° Año</t>
         </is>
       </c>
-      <c r="E31" s="10">
-        <f>IF(B31="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F31" s="10">
-        <f>IF(C31="SI", "APROBADO", IF(B31="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G31" s="11">
-        <f>IF(C31="SI", "🟢 Aprobada", IF(B31="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="E30" s="10">
+        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Historia de América IV (Siglo XX y Actual)</t>
+          <t>Historia Americana Contemporánea</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1545,7 +1518,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1564,7 +1537,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Historia Argentina III (Siglo XX y Actual)</t>
+          <t>Construcción de la Práctica Docente 2 / Residencia Media y Superior</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1552,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1598,7 +1571,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Historiografía</t>
+          <t>Historia Contemporánea</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1613,7 +1586,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1632,7 +1605,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de la Historia II</t>
+          <t>Filosofía</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1647,7 +1620,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>Tramo Superior / Seminarios</t>
         </is>
       </c>
       <c r="E35" s="10">
@@ -1663,44 +1636,17 @@
         <v/>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>Educación Sexual Integral (ESI)</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D36" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E36" s="10">
-        <f>IF(B36="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F36" s="10">
-        <f>IF(C36="SI", "APROBADO", IF(B36="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G36" s="11">
-        <f>IF(C36="SI", "🟢 Aprobada", IF(B36="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Teoría e Historia de la historiografía</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1715,7 +1661,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>5° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1734,7 +1680,7 @@
     <row r="38" ht="20" customHeight="1">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Residencia y Construcción de la Práctica Docente II</t>
+          <t>Historia de la Educación Argentina</t>
         </is>
       </c>
       <c r="B38" s="9" t="inlineStr">
@@ -1749,7 +1695,7 @@
       </c>
       <c r="D38" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>5° Año</t>
         </is>
       </c>
       <c r="E38" s="10">
@@ -1765,17 +1711,44 @@
         <v/>
       </c>
     </row>
-    <row r="39" ht="22" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
-        </is>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>DDHH, Sociedad y Estado</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E39" s="10">
+        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F39" s="10">
+        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="11">
+        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Historia Argentina y Latinoamericana</t>
+          <t>Historia del Arte</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1790,7 +1763,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>5° Año</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1809,7 +1782,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Historia Mundial Contemporánea</t>
+          <t>Sistema y política educativa</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1824,7 +1797,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>5° Año</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1843,7 +1816,7 @@
     <row r="42" ht="20" customHeight="1">
       <c r="A42" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Histórica</t>
+          <t>Lengua Extranjera</t>
         </is>
       </c>
       <c r="B42" s="9" t="inlineStr">
@@ -1858,7 +1831,7 @@
       </c>
       <c r="D42" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>5° Año</t>
         </is>
       </c>
       <c r="E42" s="10">
@@ -1874,26 +1847,299 @@
         <v/>
       </c>
     </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Esi</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E43" s="10">
+        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Nuevas Tecnologías</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E44" s="10">
+        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F44" s="10">
+        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Historia de Asia</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E45" s="10">
+        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Historia de África</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Historia del Pensamiento Social y Económico</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Historia del Pensamiento Político</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
+        <is>
+          <t>Historia de las Mujeres y de género</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E49" s="10">
+        <f>IF(B49="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F49" s="10">
+        <f>IF(C49="SI", "APROBADO", IF(B49="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G49" s="11">
+        <f>IF(C49="SI", "🟢 Aprobada", IF(B49="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Historia Americana desde los Orígenes</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E50" s="10">
+        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F50" s="10">
+        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="11">
+        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="16">
     <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A36:G36"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="I15:J15"/>
+    <mergeCell ref="A21:G21"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A39:G39"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A29:G29"/>
     <mergeCell ref="I13:J13"/>
     <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B38 B40 B41 B42 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C38 C40 C41 C42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B22 B23 B24 B25 B26 B27 B28 B30 B32 B33 B34 B35 B37 B38 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B49 B50 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C22 C23 C24 C25 C26 C27 C28 C30 C32 C33 C34 C35 C37 C38 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C49 C50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
